--- a/human_resources_forms/002_social_emotional_learning_in_the_workplace_test_form--human_resources_forms.xlsx
+++ b/human_resources_forms/002_social_emotional_learning_in_the_workplace_test_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Workplace Test 1</t>
+          <t>Communication Skills</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Workplace Test 2</t>
+          <t>Conflict Resolution</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Emotional Intelligence Test 1</t>
+          <t>Collaborative Skills</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Emotional Intelligence Test 2</t>
+          <t>Emotional Intelligence</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Social Skills Test 1</t>
+          <t>Stress Management</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Social Skills Test 2</t>
+          <t>Time Management</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Workplace Test 3</t>
+          <t>Feedback and Criticism</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Empathy</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Prioritization</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Trust Building</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Test 4</t>
+          <t>Change Management</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Test 5</t>
+          <t>Relationship Building</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Workplace Test 6</t>
+          <t>Emotional Intelligence Test</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emotional Intelligence Test 2</t>
+          <t>Social Skills Test</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Social Skills Test 3</t>
+          <t>Emotional Intelligence Test 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Workplace Test 7</t>
+          <t>Workplace Test 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Workplace Test 8</t>
+          <t>Workplace Test 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Test 9</t>
+          <t>Emotional Intelligence Test 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emotional Intelligence Test 2</t>
+          <t>Social Skills Test 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -962,126 +962,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Social Skills Test 4</t>
+          <t>Workplace Test 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>workplace_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Workplace Test 9</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>workplace_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Emotional Intelligence Test 1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>workplace_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Social Skills Test 5</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>workplace_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Workplace Test 10</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>workplace_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Workplace Test 11</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,459 +1011,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>workplace_8_choices</t>
+          <t>workplace_13_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>workplace_8_choices</t>
+          <t>workplace_13_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>workplace_8_choices</t>
+          <t>workplace_13_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>workplace_9_choices</t>
+          <t>workplace_14_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>workplace_9_choices</t>
+          <t>workplace_14_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>workplace_9_choices</t>
+          <t>workplace_14_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>workplace_10_choices</t>
+          <t>workplace_15_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'very_good'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Very Good'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>workplace_10_choices</t>
+          <t>workplace_15_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'average'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Average'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>workplace_10_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'value':_'poor'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'value': 'Poor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>workplace_11_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'value':_'very_good'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'value': 'Very Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>workplace_11_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'value':_'average'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'value': 'Average'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>workplace_11_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'value':_'poor'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'value': 'Poor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>workplace_12_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'value':_'very_good'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'value': 'Very Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>workplace_12_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'value':_'average'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'value': 'Average'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>workplace_12_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'value':_'poor'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'value': 'Poor'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>workplace_13_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>workplace_13_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>workplace_14_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>workplace_14_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>workplace_15_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>workplace_15_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>workplace_18_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>workplace_18_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>workplace_19_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>workplace_19_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>workplace_20_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>workplace_20_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
